--- a/www/download/COUNTRY.TWN.EXI382.xlsx
+++ b/www/download/COUNTRY.TWN.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>China: Taiwan</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1297</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>14.932</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>9.197</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>9.475</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>9.431</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>9.171</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>8.684</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>9.203</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>8.538</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>8.907</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>9.463</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>9.672</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>9.619</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>10.11</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>10.086</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>10.047</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>10.277</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>10.107</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>10.708</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>10.858</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>10.758</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>10.863</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>12.458</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>12.401</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13.345</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>13.402</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14.022</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>14.046</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>10.195</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6.198</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>6.349</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>6.344</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>6.306</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>6.095</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6.357</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>6.096</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>5.92</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>6.095</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>6.306</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>6.237</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>6.395</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>6.549</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>6.827</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>7.083</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>7.178</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>7.475</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>7.596</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>7.433</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>7.626</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8.727</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>8.611</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>9.257</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>9.261</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>9.609</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>9.646</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>30923.318</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>21349.979</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>21875.572</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>21831.93</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>20873.63</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>19691.231</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20833.696</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>18437.834</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>19363.382</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>20515.082</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>21075.76</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>20870.053</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>21768.6</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>21628.44</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>21489.457</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>21955.43</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>21610.171</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>22882.791</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>23201.57</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>22883.197</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>23094.788</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>26403.188</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>26190.337</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>28138.035</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>28164.847</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>29401.468</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>29432.569</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21396.9</t>
+          <t>113820309189.769</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7479.947</t>
+          <t>56785419472.7672</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7497.218</t>
+          <t>58002814768.9874</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7620.876</t>
+          <t>54871514644.1647</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7421.372</t>
+          <t>59353047054.8122</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6998.843</t>
+          <t>62807303550.0848</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7600.543</t>
+          <t>60466061783.9998</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6702.546</t>
+          <t>64166359117.8152</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5948.014</t>
+          <t>61546494747.6589</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6007.225</t>
+          <t>78016552987.48</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6660.599</t>
+          <t>81277621750.2007</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5896.482</t>
+          <t>80679127276.2815</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5975.527</t>
+          <t>67709214426.7406</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6429.814</t>
+          <t>72970316111.3609</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7311.324</t>
+          <t>70099973209.8886</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>8452.238</t>
+          <t>76471867407.086</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>8628.646</t>
+          <t>84806059587.8652</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>9218.519</t>
+          <t>83356628327.5616</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>9414.297</t>
+          <t>90698620760.0861</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>15889.465</t>
+          <t>98954480260.4958</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>16303.095</t>
+          <t>100695587376.413</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>18605.501</t>
+          <t>155960983779.169</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>18300.578</t>
+          <t>99946114890.0797</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>19659.765</t>
+          <t>104781714514.386</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>19615.25</t>
+          <t>96659555293.0612</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20324.384</t>
+          <t>105651330489.354</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>20400.498</t>
+          <t>132840912291.614</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>21453789978.5261</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>15393450395.8408</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>17986120669.8233</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>19765814139.9946</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>17039243612.5103</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>23381234129.5133</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20456684521.8505</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>19790201364.5294</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>16651327038.348</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>19379739205.8782</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>17715538938.5835</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>15595124328.8852</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>12129516700.5841</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>12693677450.3385</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>10035733760.6096</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>14265412728.8747</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>13823132187.2783</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>16279976939.9486</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>15233372256.0585</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>14367120001.335</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>12684775706.0818</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>16101859238.2639</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>13380548058.5507</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12339190799.103</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>13340868367.0095</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13204101843.8288</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>12368112649.8485</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>45631964.9436493</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>19276281.4316062</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>19292912.1635728</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>16854685.3371351</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>16393878.3923213</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>13507308.1906608</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>14719681.3213898</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>15957773.203811</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>17967730.5024808</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>20091279.761967</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>18325944.1150734</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>16349144.695494</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>13776546.7613746</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>15415563.2596341</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>16967237.6893515</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>13674254.8769271</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>15424811.4015414</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>11921359.9927996</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>12762248.895663</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>12175772.3965051</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>11201050.5313553</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>15618945.0123119</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>10380811.5230839</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11672138.194238</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>10656529.7097281</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10673140.0362287</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>16202343.3092179</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>62723.3523375914</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>102135.575491153</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>111712.850525367</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>114928.25951292</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>115487.607871226</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>135865.55043306</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>136156.174011587</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>109924.850729575</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>110735.647434274</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>114233.182327732</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>125303.718043012</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>128633.471577937</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>142319.368272282</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>140356.833545414</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>132575.441775352</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>158911.878238987</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>158006.690032979</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>198112.385378625</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>194523.805316731</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>192177.968625225</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>221745.356466685</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>231000.562947564</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>243594.009115919</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>249420.305786395</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>258234.639331617</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>261501.546994986</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>251644.784774334</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>424276.885196284</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>431516.515520334</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>480067.489877926</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>466898.481833599</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>532711.097354966</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>673847.844311259</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>651385.856697027</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>670065.977249113</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>590402.079359885</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>731360.074188279</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>816821.549133869</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>867325.620794456</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>754139.281983696</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>816647.988070798</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>786181.651605462</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>989038.170857583</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1141855.14140808</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1238791.95467867</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1316669.9954718</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1486913.6544806</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>1709221.71636553</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2412940.65515486</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1634827.66126587</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1666915.1583319</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1638366.96765181</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1703570.33750651</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2102959.3379892</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.00265174182861216</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.514082511220574</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.583166506128234</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.61444157746179</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.564454147803086</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.700664100054662</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.628456748605236</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.661319983736118</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.642790406656013</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.69002549228454</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.624025049247287</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.621902194837065</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.507356506651186</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.493463297364886</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.271470932329526</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.407501329219562</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.375782139453425</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.433751075077636</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.381995221954012</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.105960353430077</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.285249009154088</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.155487753117259</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.367700173353489</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.5932783113904</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.470312814957914</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.539247780090064</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.64944306144609</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2104.35568365559</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2483.57567574557</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2832.81683831365</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3115.47414097276</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2702.19699835187</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3836.07063534902</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3217.77527320268</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3246.37085423871</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2812.96174311129</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>3179.66483549781</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2809.22567292248</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2500.42076781919</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1896.6001658358</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1938.40993362367</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1469.96334670315</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2014.06383386348</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1925.65643977442</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2177.86506581012</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2005.52579170548</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1932.82530572727</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1663.25576282866</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1845.14115867313</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1553.9661638063</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1332.99656150778</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1440.54028737375</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1374.14458225758</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1282.14764975978</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>26912522039.2846</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>11321763484.8215</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>14374901183.6228</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>13797926959.0583</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>17009311855.4559</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>19699267384.1819</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>17807299084.1377</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>17522129468.5518</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>13676803669.7711</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>15971490194.232</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>15212209072.1798</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>11176796797.0116</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>7387746339.64253</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>9500854383.27238</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>8868065057.78814</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>11597113526.8366</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>7312769900.76181</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>9480176354.22029</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>9603264105.07043</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>13928231176.4663</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>15107906939.9087</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>5969898067.16991</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>13134070483.999</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>12423595779.2225</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>13748372564.6256</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>14670479856.3995</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>7565401941.88401</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>26852201543.4665</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>11081051778.694</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>14267106827.6253</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>13720676461.2876</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>16903343518.5169</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>19656554154.7041</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>17789862193.2083</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>17614603610.0857</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>13892372795.2436</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>16696750865.6137</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>16157655437.5905</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>12157103785.1511</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>8356721177.4277</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>10721678628.389</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>9874331989.94818</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>12896426321.6777</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>8234741378.27439</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>10521302236.1874</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>10830293409.6373</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>15064401713.9156</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>16482273505.6989</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>7492586851.67651</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>15108562446.8477</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14487705001.8851</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>15743071967.9396</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16876699777.5417</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>13103429970.3214</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>60320495.8181174</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>240711706.127431</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>107794355.997454</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>77250497.770628</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>105968336.938979</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>42713229.4778138</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>17436890.9294276</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-92474141.5338472</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-215569125.472549</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-725260671.381714</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-945446365.410695</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-980306988.13947</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-968974837.78517</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-1220824245.11659</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-1006266932.16005</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-1299312794.84109</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-921971477.512585</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-1041125881.96713</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-1227029304.5669</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-1136170537.4493</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-1374366565.79019</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-1522688784.5066</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-1974491962.84878</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-2064109222.66258</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-1994699403.31394</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-2206219921.14221</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-5538028028.43741</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>2098.77547566697</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>1206.81285555195</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1180.81294021305</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>1201.19729525204</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>1176.93069445111</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>1148.27365588608</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>1195.5426872634</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>1099.48093371216</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>1004.81692034898</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>985.615042083593</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>1056.19848403028</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>945.403604296256</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>934.347731183286</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>981.875776132885</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>1070.91102648342</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>1193.33014443106</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>1202.02914298373</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.931</t>
+          <t>1233.21375214095</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>1239.42452176845</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.987</t>
+          <t>2137.62815824072</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>2137.69782114536</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>2132.03801161939</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>2125.35979162334</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>1.232</t>
+          <t>2123.83451060833</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>1.303</t>
+          <t>2118.04484498879</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2115.14899776277</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>2114.82954464568</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>2070.94512521157</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>2321.43206080241</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>2308.84061342275</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>2314.83783995827</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>2276.09695119231</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>2267.47777803334</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>2263.72018732469</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>2159.50268915445</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>2173.87788443221</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>2167.92577406703</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>2179.02628798238</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>2169.62458832307</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>2153.06862766499</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>2144.31710818515</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>2138.97801843479</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>2136.44878656302</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>2138.16021134038</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>2136.9010645849</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>2136.83765369008</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>2127.12152083808</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>2126.00360507735</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>2119.44240532064</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>2112.01120651262</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>2108.55987001431</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>2101.52882282517</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>2096.77104617741</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>2095.41693739671</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>117542.410384828</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>127132.466742488</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>153714.686274414</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>143374.055501534</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>162562.318469462</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>230300.687086305</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>198706.660679766</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>199848.624740803</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>182316.993925878</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>206485.929339925</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>225292.489028664</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>249367.885864684</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>250578.475303703</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>246982.673540721</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>205113.673851279</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>296367.526054134</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>315716.853141663</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>344553.545126307</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>332098.621830571</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>340825.462004606</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>368091.425579536</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>355638.684238742</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>373046.476117729</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>371324.012394534</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>381613.884198779</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>387569.219283527</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>390743.684142504</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>38814192954.7265</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>20138774942.8152</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>20429649602.8022</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>19688935263.9189</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20944950368.8074</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>23639005151.0307</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>22757464264.9229</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>24314091204.2415</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>22307150596.8732</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>27492556989.9334</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>28985446039.9738</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>32338387284.6376</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>28194355620.338</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>28787101694.2606</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>25116119432.897</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>30018414065.5015</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>33841672732.7462</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>33375688505.0005</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>35223052173.6523</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>35356159608.3846</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>32767884585.4427</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>43177791643.9003</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>30592258503.6729</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>32247809196.2788</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>28836643538.1149</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>31159489093.0525</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>35260555051.7114</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>113735.495562069</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>118190.409024355</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>147673.37605329</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>140659.587081349</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>154486.518148973</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>222002.325793256</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>178879.619644813</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>174228.845544564</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>160938.073628184</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>195982.672584035</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>211358.140435367</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>229702.861121657</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>223948.455025546</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>230167.1354848</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>176547.619997078</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>269287.500866024</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>288037.649866149</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>311135.228499488</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>291994.862422043</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>293387.670967909</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>297362.805013331</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>285485.803418775</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>293946.673531061</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>304292.63809713</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>316216.217599923</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>322895.038981392</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>326417.241386724</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>30923.318</t>
+          <t>63569997854.6215</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21349.979</t>
+          <t>29644066270.367</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21875.572</t>
+          <t>33673691717.3166</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>21831.93</t>
+          <t>32975460931.4922</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20873.63</t>
+          <t>36472805975.5428</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>19691.231</t>
+          <t>42050859964.5948</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20833.696</t>
+          <t>37367078224.8426</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18437.834</t>
+          <t>37549172050.5055</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>19363.382</t>
+          <t>32352153375.2834</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>20515.082</t>
+          <t>41537856590.8968</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>21075.76</t>
+          <t>41867127167.8519</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>20870.053</t>
+          <t>40589191627.5742</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>21768.6</t>
+          <t>32275122022.7895</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>21628.44</t>
+          <t>35983565681.7456</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>21489.457</t>
+          <t>29779506746.1963</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>21955.43</t>
+          <t>38276505882.8944</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>21610.171</t>
+          <t>37962594401.4967</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>22882.791</t>
+          <t>39212224641.2396</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>23201.57</t>
+          <t>40232287997.1009</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>22883.197</t>
+          <t>44241464580.9369</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>23094.788</t>
+          <t>41038817665.1195</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26403.188</t>
+          <t>41707518479.6637</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>26190.337</t>
+          <t>36107217922.5439</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>28138.035</t>
+          <t>38009176380.9231</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>28164.847</t>
+          <t>36616340707.429</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>29401.468</t>
+          <t>39553900707.3432</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>29432.569</t>
+          <t>36558305284.4348</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21396.9</t>
+          <t>3806.91482275887</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7479.947</t>
+          <t>8942.05771813301</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7497.218</t>
+          <t>6041.31022112361</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>7620.876</t>
+          <t>2714.46842018437</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7421.372</t>
+          <t>8075.80032048927</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6998.843</t>
+          <t>8298.36129304894</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7600.543</t>
+          <t>19827.0410349535</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6702.546</t>
+          <t>25619.7791962383</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5948.014</t>
+          <t>21378.9202976936</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6007.225</t>
+          <t>10503.25675589</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6660.599</t>
+          <t>13934.3485932969</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5896.482</t>
+          <t>19665.0247430273</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5975.527</t>
+          <t>26630.0202781575</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6429.814</t>
+          <t>16815.5380559211</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>7311.324</t>
+          <t>28566.0538542007</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>8452.238</t>
+          <t>27080.0251881096</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>8628.646</t>
+          <t>27679.2032755139</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>9218.519</t>
+          <t>33418.3166268187</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>9414.297</t>
+          <t>40103.7594085272</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>15889.465</t>
+          <t>47437.7910366969</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>16303.095</t>
+          <t>70728.6205662054</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>18605.501</t>
+          <t>70152.8808199667</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>18300.578</t>
+          <t>79099.8025866684</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>19659.765</t>
+          <t>67031.3742974041</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>19615.25</t>
+          <t>65397.6665988561</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20324.384</t>
+          <t>64674.1803021352</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>20400.498</t>
+          <t>64326.4427557798</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>73633.534</t>
+          <t>-24755804899.895</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>39913.154</t>
+          <t>-9505291327.55176</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>41080.063</t>
+          <t>-13244042114.5144</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>39089.878</t>
+          <t>-13286525667.5733</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>41332.001</t>
+          <t>-15527855606.7354</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>43572.087</t>
+          <t>-18411854813.564</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>41949.395</t>
+          <t>-14609613959.9197</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>43370.47</t>
+          <t>-13235080846.2641</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>41816.059</t>
+          <t>-10045002778.4102</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>52541.498</t>
+          <t>-14045299600.9634</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>54255.66</t>
+          <t>-12881681127.8781</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>55349.708</t>
+          <t>-8250804342.93661</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>47632.066</t>
+          <t>-4080766402.45149</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>50041.972</t>
+          <t>-7196463987.48506</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>47338.981</t>
+          <t>-4663387313.29925</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>52274.411</t>
+          <t>-8258091817.39286</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>54381.461</t>
+          <t>-4120921668.75048</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>56287.852</t>
+          <t>-5836536136.23909</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>60998.437</t>
+          <t>-5009235823.44857</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>66107.072</t>
+          <t>-8885304972.55225</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>64164.027</t>
+          <t>-8270933079.67675</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>93402.686</t>
+          <t>1470273164.2366</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>66331.285</t>
+          <t>-5514959418.87104</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>66644.816</t>
+          <t>-5761367184.64439</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>62573.573</t>
+          <t>-7779697169.31408</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>67650.907</t>
+          <t>-8394411614.29071</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>82946.891</t>
+          <t>-1297750232.7234</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>87776.2112279376</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>92669.9296631134</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>108709.168858935</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>99906.9967374423</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>119021.892824238</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>139012.032182184</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>96091.9446708882</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>116084.756293815</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>101091.165927465</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>99156.8681809437</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>94254.5147663371</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>92113.8471126256</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>81410.0292862153</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>76012.7013314484</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>71882.1041848999</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>85922.3601927722</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>114106.968971797</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>118417.276059697</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>109408.84071858</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>106482.653306359</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>118648.427812057</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>127228.278360083</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>122987.662170685</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>125184.918820729</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>135091.612303707</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>135858.017271863</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>138501.954999248</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>16826.727</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>13440.532</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>13497.393</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>13506.764</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>12867.277</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>12663.614</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>12638.941</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>10526.542</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>11543.643</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>12185.624</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>12468.315</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>11965.559</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>12777.922</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>12541.367</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>11821.104</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>12286.976</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>11735.223</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>13330.713</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>13399.744</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>12789.492</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>13063.711</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>14930.775</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>14892.258</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15678.475</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>15235.198</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16217.696</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>15896.039</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>136603.736699757</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>158791.542359171</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>174425.136865166</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>177440.342504896</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>174549.874891059</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>248111.774763851</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>216421.623780419</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>204302.333488545</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>186836.78812236</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>182824.514112269</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>179157.793449945</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>181078.259997336</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>148854.757844004</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>144583.193589917</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>132568.841012229</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>164617.235781039</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>208047.374256571</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>226697.224774669</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>197282.404688934</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>213157.950012757</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>206278.94565608</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>233190.110439203</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>236818.20663597</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>212214.424283913</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>255784.870041069</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>225842.970558483</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>244548.640377083</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>18225.031</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>14012.49</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>16453.4</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>18188.986</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>15535.946</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>21623.183</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>18660.341</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>17911.12</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>15156.076</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>17276.157</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>15918.144</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>14009.099</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>11033.193</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>11342.909</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>8974.859</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>12831.147</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>12362.095</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>14736.199</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>13623.746</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>12535.612</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>10974.648</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>13607.538</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>11505.127</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10614.195</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>11497.899</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11540.619</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>10541.177</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-46.62</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-54.43</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-58.1</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-52.23</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-67.63</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-59.27</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-62.58</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-60.75</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-65.23</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-58.16</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-57.91</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-45.84</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-43.31</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-18.54</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-34.13</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-30.2</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-37.44</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-30.9</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>26.75</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>48.55</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>36.73</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>59.06</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>85.22</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>70.6</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>76.11</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>93.53</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>39.641</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>17.934</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>18.17</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>15.735</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>15.135</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>12.501</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>13.573</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>14.492</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>16.16</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>18.185</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>15.965</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>14.68</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>12.603</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>13.682</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>15.23</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>12.226</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>12.372</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>10.764</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>11.454</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>14.931</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>11.622</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>13.559</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>13.206</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10.413</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>9.529</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>9.548</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>16.845</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>81158.8758045633</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>76587.7392705933</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>102144.364419717</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>85731.4421538221</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>119821.196877652</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>122955.249771536</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>124218.600197402</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>117075.857778359</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>95082.2983952718</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>107642.358856927</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>128002.738222096</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>132858.267403766</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>146328.974877131</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>144893.879316792</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>145228.760091941</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>171746.301299082</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>141664.661346563</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>160685.898540808</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>184301.893317498</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>178850.544140208</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>249093.834173894</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>233606.163594249</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>257114.33592939</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>279096.87181187</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>280540.667956874</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>318070.468613949</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>315166.245268054</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>21396900066.2578</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>7479946759.99764</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>7497217520.00165</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>7620876119.99979</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>7421371880.00161</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6998842759.99053</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7600543080.00527</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6702545720.00431</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5948013760.00604</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6007225119.99611</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6660598879.99171</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5896482279.99458</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5975527480.00854</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6429813520.00817</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>7311323760.00602</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>8452238079.99259</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>8628645999.99539</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>9218519440.00674</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>9414296839.99738</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>15889465114.4487</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>16303095407.5834</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>18605501152.2319</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>18300577899.2445</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>19659765080.3188</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>19615249722.6807</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>20324384451.1966</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20400497593.4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>30923317559.3836</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>21349978519.9956</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>21875572159.9982</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>21831930120.0037</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20873629919.9972</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>19691230519.9955</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20833696000.0013</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>18437833960.0038</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>19363382480.0036</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>20515081599.9971</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>21075760159.9942</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>20870052839.9952</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>21768600360.0037</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>21628440080.0004</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>21489456560.0043</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>21955429599.9976</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>21610171439.997</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>22882791360.0062</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>23201569560.0004</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>22883196905.3845</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>23094788338.7557</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26403187985.8109</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>26190337351.4304</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>28138034845.0882</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>28164847143.1681</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>29401467595.118</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>29432569199.6184</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>16826727086.9132</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>13440531911.8876</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>13497393414.3846</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>13506764147.3701</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>12867277325.8582</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>12663613811.4688</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12638941336.2515</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>10526541694.9589</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>11543643190.7242</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>12185624340.9121</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>12468314786.4952</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>11965559389.2409</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>12777921603.6575</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>12541367470.2039</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>11821103809.486</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>12286975811.6268</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>11735223045.6256</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>13330713371.7834</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>13399743981.3375</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>12789492480.2946</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>13063711222.2542</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>14930775431.1644</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>14892257696.9264</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15678474782.8162</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>15235198152.7272</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16217696303.3315</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>15896038586.6582</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>14931983.0752273</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>9196900.0000008</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>9474700.00000072</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>9431300.00000228</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>9170800.00000123</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>8684199.99999927</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>9203299.99999823</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>8538000.00000143</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>8907300.00000028</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9463000.00000034</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>9672099.9999999</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>9619199.99999904</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>10110499.9999985</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10086400.0000008</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>10046599.9999987</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>10276600.0000019</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>10106900.0000004</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>10708400.0000024</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>10857899.9999995</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>10757823.0398273</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>10863005.2571879</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>12457610.5109195</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>12400662.1132831</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13344669.6227304</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>13402075.1165835</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14022259.4396843</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>14046163.6413919</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10194944.7734318</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6198100.0000009</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>6349200.00000081</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6344400.00000228</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6305700.00000107</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6095099.99999936</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>6357399.99999744</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6096100.00000147</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>5919500.00000028</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6094900.00000083</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>6306199.99999994</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>6236999.99999876</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>6395399.99999889</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>6548500.00000201</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>6827199.99999854</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>7082900.00000152</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>7178400.00000084</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>7475200.00000219</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>7595700.00000062</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>7433222.21556335</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>7626473.3239277</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>8726627.31660215</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>8610578.76947349</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>9256731.15401428</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>9261017.19191152</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>9608961.10519592</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>9646402.77753172</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>30923317559.3836</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>21349978519.9956</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>21875572159.9982</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>21831930120.0037</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>20873629919.9972</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>19691230519.9955</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20833696000.0013</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>18437833960.0038</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>19363382480.0036</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>20515081599.9971</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>21075760159.9942</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>20870052839.9952</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>21768600360.0037</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>21628440080.0004</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>21489456560.0043</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>21955429599.9976</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>21610171439.997</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>22882791360.0062</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>23201569560.0004</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>22883196905.3845</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>23094788338.7557</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26403187985.8109</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>26190337351.4304</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>28138034845.0882</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>28164847143.1681</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>29401467595.118</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>29432569199.6184</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>21396900066.2578</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>7479946759.99764</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>7497217520.00165</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>7620876119.99979</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>7421371880.00161</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6998842759.99053</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7600543080.00527</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>6702545720.00431</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5948013760.00604</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6007225119.99611</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>6660598879.99171</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5896482279.99458</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5975527480.00854</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6429813520.00817</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>7311323760.00602</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>8452238079.99259</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>8628645999.99539</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>9218519440.00674</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>9414296839.99738</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>15889465114.4487</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>16303095407.5834</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>18605501152.2319</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>18300577899.2445</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>19659765080.3188</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>19615249722.6807</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>20324384451.1966</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>20400497593.4762</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>475263.542590576</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>491001.056995797</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>587091.90414845</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>547843.938566553</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>628608.206751655</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>819205.170695925</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>738777.813417273</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>723573.730454305</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>654348.199876359</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>697878.72323561</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>759637.08724241</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>804577.896172103</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>770957.050519986</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>775674.029371982</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>699219.279455981</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>912822.672753282</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>951359.974829111</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1052126.69145145</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>1055389.74583558</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1115539.11726456</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>1297715.01317107</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>1324491.74875614</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>1413819.35475018</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1392125.47837996</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1471999.60259108</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>1502034.85560687</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1511549.20031377</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>156486.615581622</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>175669.367950381</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>194709.651407188</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>193978.010886309</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>195088.992113511</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>274271.974272982</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>235338.043492557</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>226557.097189863</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>202183.774451127</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>198043.487418386</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>199150.171416948</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>196973.473133267</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>164271.619960723</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>159243.000176709</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>144314.497578266</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>181772.801576617</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>225527.191484974</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>243949.220790373</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>214091.114094722</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>230849.621579195</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>224988.649351701</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>251339.95735394</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>254827.746856389</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>238505.043280387</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>274259.997078361</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>247454.493276498</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>262200.809324289</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
